--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83620AA4-AA0C-4E2D-B2E4-E52351F27643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C74457F-7DA0-476C-93A6-55910A59620B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1421,26 +1421,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B15" s="14">
+        <v>480</v>
+      </c>
+      <c r="C15" s="14">
+        <v>15</v>
+      </c>
+      <c r="D15" s="14">
+        <v>120</v>
+      </c>
+      <c r="E15" s="14">
+        <v>30</v>
+      </c>
+      <c r="F15" s="14">
+        <v>300</v>
+      </c>
+      <c r="G15" s="14">
+        <v>6</v>
+      </c>
+      <c r="H15" s="14">
+        <v>40</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>985</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>455</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C74457F-7DA0-476C-93A6-55910A59620B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE44D6D4-C350-446B-895B-7B48E04C156B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>High</t>
+  </si>
+  <si>
+    <t>not satisfield</t>
   </si>
 </sst>
 </file>
@@ -1467,24 +1470,44 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B16" s="14">
+        <v>480</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14">
+        <v>0</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>30</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>510</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
+        <v>930</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>64</v>
+      </c>
       <c r="M16" s="16"/>
       <c r="N16" s="17"/>
     </row>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE44D6D4-C350-446B-895B-7B48E04C156B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEDE3CF-1558-4D22-951E-BB427CEE0609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -231,7 +231,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>not satisfield</t>
+    <t>Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -1508,30 +1508,58 @@
       <c r="L16" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B17" s="14">
+        <v>480</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>180</v>
+      </c>
+      <c r="E17" s="14">
+        <v>20</v>
+      </c>
+      <c r="F17" s="14">
+        <v>200</v>
+      </c>
+      <c r="G17" s="14">
+        <v>4</v>
+      </c>
+      <c r="H17" s="14">
+        <v>30</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEDE3CF-1558-4D22-951E-BB427CEE0609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405BF2A5-0088-4060-93EC-8EE0C73FBB04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1562,26 +1562,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B18" s="14">
+        <v>480</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>250</v>
+      </c>
+      <c r="E18" s="14">
+        <v>60</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>30</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405BF2A5-0088-4060-93EC-8EE0C73FBB04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF97A16D-D6FB-41C9-8626-CB54A09C89D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1608,48 +1608,96 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B19" s="14">
+        <v>480</v>
+      </c>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>300</v>
+      </c>
+      <c r="E19" s="14">
+        <v>60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>40</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B20" s="14">
+        <v>480</v>
+      </c>
+      <c r="C20" s="14">
+        <v>15</v>
+      </c>
+      <c r="D20" s="14">
+        <v>60</v>
+      </c>
+      <c r="E20" s="14">
+        <v>30</v>
+      </c>
+      <c r="F20" s="14">
+        <v>250</v>
+      </c>
+      <c r="G20" s="14">
+        <v>5</v>
+      </c>
+      <c r="H20" s="14">
+        <v>30</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>865</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>575</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF97A16D-D6FB-41C9-8626-CB54A09C89D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E227DA6E-9908-4F20-B0E0-E8BCB3566CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1700,26 +1700,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B21" s="14">
+        <v>480</v>
+      </c>
+      <c r="C21" s="14">
+        <v>15</v>
+      </c>
+      <c r="D21" s="14">
+        <v>60</v>
+      </c>
+      <c r="E21" s="14">
+        <v>0</v>
+      </c>
+      <c r="F21" s="14">
+        <v>300</v>
+      </c>
+      <c r="G21" s="14">
+        <v>6</v>
+      </c>
+      <c r="H21" s="14">
+        <v>30</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>885</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>555</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E227DA6E-9908-4F20-B0E0-E8BCB3566CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15514CA0-8B06-4270-8E5B-4EBFC7890A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1746,26 +1746,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B22" s="14">
+        <v>480</v>
+      </c>
+      <c r="C22" s="14">
+        <v>15</v>
+      </c>
+      <c r="D22" s="14">
+        <v>180</v>
+      </c>
+      <c r="E22" s="14">
+        <v>35</v>
+      </c>
+      <c r="F22" s="14">
+        <v>250</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="14">
+        <v>20</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15514CA0-8B06-4270-8E5B-4EBFC7890A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA7165B-2A85-484E-B845-E1F0E335FB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1792,26 +1792,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B23" s="14">
+        <v>480</v>
+      </c>
+      <c r="C23" s="14">
+        <v>15</v>
+      </c>
+      <c r="D23" s="14">
+        <v>300</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
+        <v>250</v>
+      </c>
+      <c r="G23" s="14">
+        <v>5</v>
+      </c>
+      <c r="H23" s="14">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1045</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>395</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA7165B-2A85-484E-B845-E1F0E335FB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D8333B-CC7E-4ADE-B778-0CD40529B378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1838,26 +1838,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B24" s="14">
+        <v>480</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>300</v>
+      </c>
+      <c r="E24" s="14">
+        <v>60</v>
+      </c>
+      <c r="F24" s="14">
+        <v>200</v>
+      </c>
+      <c r="G24" s="14">
+        <v>4</v>
+      </c>
+      <c r="H24" s="14">
+        <v>60</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D8333B-CC7E-4ADE-B778-0CD40529B378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E940AD-25A1-42C3-8A37-D9A586AFAD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1884,26 +1884,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B25" s="14">
+        <v>480</v>
+      </c>
+      <c r="C25" s="14">
+        <v>10</v>
+      </c>
+      <c r="D25" s="14">
+        <v>300</v>
+      </c>
+      <c r="E25" s="14">
+        <v>60</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>60</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E940AD-25A1-42C3-8A37-D9A586AFAD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7124454D-FD20-4141-BA46-07DB2D05078D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1930,26 +1930,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B26" s="14">
+        <v>480</v>
+      </c>
+      <c r="C26" s="14">
+        <v>10</v>
+      </c>
+      <c r="D26" s="14">
+        <v>300</v>
+      </c>
+      <c r="E26" s="14">
+        <v>60</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>60</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7124454D-FD20-4141-BA46-07DB2D05078D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47450813-27E3-4A4E-AB57-7F85233C651E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1976,26 +1976,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B27" s="14">
+        <v>480</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>60</v>
+      </c>
+      <c r="F27" s="14">
+        <v>300</v>
+      </c>
+      <c r="G27" s="14">
+        <v>6</v>
+      </c>
+      <c r="H27" s="14">
+        <v>30</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47450813-27E3-4A4E-AB57-7F85233C651E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F530A1DE-D6EC-4DC1-8631-662E9EC3BEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2022,26 +2022,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B28" s="14">
+        <v>480</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>120</v>
+      </c>
+      <c r="E28" s="14">
+        <v>120</v>
+      </c>
+      <c r="F28" s="14">
+        <v>300</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="14">
+        <v>30</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F530A1DE-D6EC-4DC1-8631-662E9EC3BEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486312EF-121C-4A82-B187-25276A1C197D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2068,26 +2068,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B29" s="14">
+        <v>480</v>
+      </c>
+      <c r="C29" s="14">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
+        <v>300</v>
+      </c>
+      <c r="E29" s="14">
+        <v>60</v>
+      </c>
+      <c r="F29" s="14">
+        <v>200</v>
+      </c>
+      <c r="G29" s="14">
+        <v>4</v>
+      </c>
+      <c r="H29" s="14">
+        <v>40</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486312EF-121C-4A82-B187-25276A1C197D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C188546-037B-4793-9E15-19CC2A2787BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2114,26 +2114,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B30" s="14">
+        <v>480</v>
+      </c>
+      <c r="C30" s="14">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
+        <v>60</v>
+      </c>
+      <c r="E30" s="14">
+        <v>0</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>60</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>620</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>820</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C188546-037B-4793-9E15-19CC2A2787BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C590DD8-ACC2-4870-9926-60A4CF8F6287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2160,26 +2160,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B31" s="14">
+        <v>480</v>
+      </c>
+      <c r="C31" s="14">
+        <v>30</v>
+      </c>
+      <c r="D31" s="14">
+        <v>120</v>
+      </c>
+      <c r="E31" s="14">
+        <v>180</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>120</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C590DD8-ACC2-4870-9926-60A4CF8F6287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA65771-796B-4351-A188-53EB89B0752C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2206,26 +2206,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B32" s="14">
+        <v>480</v>
+      </c>
+      <c r="C32" s="14">
+        <v>30</v>
+      </c>
+      <c r="D32" s="14">
+        <v>120</v>
+      </c>
+      <c r="E32" s="14">
+        <v>60</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>120</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
+  <workbookPr showObjects="none"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA65771-796B-4351-A188-53EB89B0752C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B4ADC7-0968-4641-A72E-C6595C6DD85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2252,26 +2252,50 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B33" s="14">
+        <v>480</v>
+      </c>
+      <c r="C33" s="14">
+        <v>30</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120</v>
+      </c>
+      <c r="E33" s="14">
+        <v>60</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>120</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B4ADC7-0968-4641-A72E-C6595C6DD85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E7DB7A-1A32-49BB-99A0-9CB428639DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2298,26 +2298,50 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B34" s="14">
+        <v>480</v>
+      </c>
+      <c r="C34" s="14">
+        <v>30</v>
+      </c>
+      <c r="D34" s="14">
+        <v>120</v>
+      </c>
+      <c r="E34" s="14">
+        <v>60</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>60</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>690</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr showObjects="none"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E7DB7A-1A32-49BB-99A0-9CB428639DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD3EFD81-BE7E-424A-83AA-5E5BAD230D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2344,26 +2344,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B35" s="14">
+        <v>480</v>
+      </c>
+      <c r="C35" s="14">
+        <v>30</v>
+      </c>
+      <c r="D35" s="14">
+        <v>120</v>
+      </c>
+      <c r="E35" s="14">
+        <v>60</v>
+      </c>
+      <c r="F35" s="14">
+        <v>300</v>
+      </c>
+      <c r="G35" s="14">
+        <v>6</v>
+      </c>
+      <c r="H35" s="14">
+        <v>60</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD3EFD81-BE7E-424A-83AA-5E5BAD230D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D33FAB-C400-4D41-BB0D-11CA60F30F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2345,7 +2345,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13">
-        <v>46299</v>
+        <v>46301</v>
       </c>
       <c r="B35" s="14">
         <v>480</v>
@@ -2390,26 +2390,50 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B36" s="14">
+        <v>480</v>
+      </c>
+      <c r="C36" s="14">
+        <v>30</v>
+      </c>
+      <c r="D36" s="14">
+        <v>120</v>
+      </c>
+      <c r="E36" s="14">
+        <v>30</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>60</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D33FAB-C400-4D41-BB0D-11CA60F30F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C78D422-99E3-49EC-A490-4B9CF31B687C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2436,26 +2436,50 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B37" s="14">
+        <v>480</v>
+      </c>
+      <c r="C37" s="14">
+        <v>40</v>
+      </c>
+      <c r="D37" s="14">
+        <v>120</v>
+      </c>
+      <c r="E37" s="14">
+        <v>0</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>120</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>760</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>680</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C78D422-99E3-49EC-A490-4B9CF31B687C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F327D1F2-FCBD-4E63-B41F-6BBBCE1BBB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2482,26 +2482,50 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B38" s="14">
+        <v>480</v>
+      </c>
+      <c r="C38" s="14">
+        <v>40</v>
+      </c>
+      <c r="D38" s="14">
+        <v>120</v>
+      </c>
+      <c r="E38" s="14">
+        <v>60</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>30</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>710</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F327D1F2-FCBD-4E63-B41F-6BBBCE1BBB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7640C6-693F-4FB1-9CA8-A733F209DCAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2528,26 +2528,50 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B39" s="14">
+        <v>480</v>
+      </c>
+      <c r="C39" s="14">
+        <v>30</v>
+      </c>
+      <c r="D39" s="14">
+        <v>300</v>
+      </c>
+      <c r="E39" s="14">
+        <v>60</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>120</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7640C6-693F-4FB1-9CA8-A733F209DCAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD1CD68-2A23-4BAC-AEFB-E86692C93E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2574,26 +2574,50 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B40" s="14">
+        <v>480</v>
+      </c>
+      <c r="C40" s="14">
+        <v>30</v>
+      </c>
+      <c r="D40" s="14">
+        <v>300</v>
+      </c>
+      <c r="E40" s="14">
+        <v>60</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>120</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD1CD68-2A23-4BAC-AEFB-E86692C93E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647C8A0B-F82D-4942-B7FB-DED9F8003333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2620,26 +2620,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B41" s="14">
+        <v>480</v>
+      </c>
+      <c r="C41" s="14">
+        <v>20</v>
+      </c>
+      <c r="D41" s="14">
+        <v>300</v>
+      </c>
+      <c r="E41" s="14">
+        <v>60</v>
+      </c>
+      <c r="F41" s="14">
+        <v>0</v>
+      </c>
+      <c r="G41" s="14">
+        <v>0</v>
+      </c>
+      <c r="H41" s="14">
+        <v>120</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647C8A0B-F82D-4942-B7FB-DED9F8003333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041E2A61-D8A8-4DA3-AE00-A95D0571D9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2666,26 +2666,50 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B42" s="14">
+        <v>480</v>
+      </c>
+      <c r="C42" s="14">
+        <v>30</v>
+      </c>
+      <c r="D42" s="14">
+        <v>300</v>
+      </c>
+      <c r="E42" s="14">
+        <v>0</v>
+      </c>
+      <c r="F42" s="14">
+        <v>0</v>
+      </c>
+      <c r="G42" s="14">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14">
+        <v>60</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041E2A61-D8A8-4DA3-AE00-A95D0571D9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54C81B4-955B-4B71-A1F6-8056A68D6A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2712,26 +2712,50 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B43" s="14">
+        <v>480</v>
+      </c>
+      <c r="C43" s="14">
+        <v>30</v>
+      </c>
+      <c r="D43" s="14">
+        <v>300</v>
+      </c>
+      <c r="E43" s="14">
+        <v>0</v>
+      </c>
+      <c r="F43" s="14">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>120</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54C81B4-955B-4B71-A1F6-8056A68D6A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D622739D-0B2A-4C15-A5A4-CFF536DA2085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,9 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">happy day </t>
   </si>
 </sst>
 </file>
@@ -2758,26 +2761,50 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B44" s="14">
+        <v>480</v>
+      </c>
+      <c r="C44" s="14">
+        <v>40</v>
+      </c>
+      <c r="D44" s="14">
+        <v>0</v>
+      </c>
+      <c r="E44" s="14">
+        <v>0</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>120</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>640</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>800</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D622739D-0B2A-4C15-A5A4-CFF536DA2085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4129820-90DE-49D6-83BC-6A3A7E77B3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2807,26 +2807,50 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B45" s="14">
+        <v>480</v>
+      </c>
+      <c r="C45" s="14">
+        <v>30</v>
+      </c>
+      <c r="D45" s="14">
+        <v>300</v>
+      </c>
+      <c r="E45" s="14">
+        <v>60</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>120</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4129820-90DE-49D6-83BC-6A3A7E77B3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7D400E-60BA-4781-B7A0-0A4EDC985048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2853,26 +2853,50 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B46" s="14">
+        <v>480</v>
+      </c>
+      <c r="C46" s="14">
+        <v>30</v>
+      </c>
+      <c r="D46" s="14">
+        <v>300</v>
+      </c>
+      <c r="E46" s="14">
+        <v>60</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>120</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7D400E-60BA-4781-B7A0-0A4EDC985048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDE8FC9-9C6C-45B8-92F6-D1FF5ADC8A29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2899,26 +2899,50 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B47" s="14">
+        <v>480</v>
+      </c>
+      <c r="C47" s="14">
+        <v>30</v>
+      </c>
+      <c r="D47" s="14">
+        <v>300</v>
+      </c>
+      <c r="E47" s="14">
+        <v>0</v>
+      </c>
+      <c r="F47" s="14">
+        <v>120</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>0</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDE8FC9-9C6C-45B8-92F6-D1FF5ADC8A29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6B4BEB-3C64-4E5D-89BA-0EB5157B3340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2945,26 +2945,50 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B48" s="14">
+        <v>480</v>
+      </c>
+      <c r="C48" s="14">
+        <v>30</v>
+      </c>
+      <c r="D48" s="14">
+        <v>300</v>
+      </c>
+      <c r="E48" s="14">
+        <v>120</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>0</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6B4BEB-3C64-4E5D-89BA-0EB5157B3340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F58D98C-B418-4255-9387-C225FB6236EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2991,26 +2991,50 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B49" s="14">
+        <v>480</v>
+      </c>
+      <c r="C49" s="14">
+        <v>30</v>
+      </c>
+      <c r="D49" s="14">
+        <v>120</v>
+      </c>
+      <c r="E49" s="14">
+        <v>60</v>
+      </c>
+      <c r="F49" s="14">
+        <v>300</v>
+      </c>
+      <c r="G49" s="14">
+        <v>6</v>
+      </c>
+      <c r="H49" s="14">
+        <v>0</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F58D98C-B418-4255-9387-C225FB6236EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1933B83D-5CC5-40A2-A064-5D8141A0585C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3037,26 +3037,50 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B50" s="14">
+        <v>480</v>
+      </c>
+      <c r="C50" s="14">
+        <v>30</v>
+      </c>
+      <c r="D50" s="14">
+        <v>120</v>
+      </c>
+      <c r="E50" s="14">
+        <v>60</v>
+      </c>
+      <c r="F50" s="14">
+        <v>250</v>
+      </c>
+      <c r="G50" s="14">
+        <v>5</v>
+      </c>
+      <c r="H50" s="14">
+        <v>0</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1933B83D-5CC5-40A2-A064-5D8141A0585C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B872C43-16D0-444C-9E7A-5E2B7C3E753B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3083,26 +3083,50 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B51" s="14">
+        <v>480</v>
+      </c>
+      <c r="C51" s="14">
+        <v>20</v>
+      </c>
+      <c r="D51" s="14">
+        <v>120</v>
+      </c>
+      <c r="E51" s="14">
+        <v>0</v>
+      </c>
+      <c r="F51" s="14">
+        <v>200</v>
+      </c>
+      <c r="G51" s="14">
+        <v>4</v>
+      </c>
+      <c r="H51" s="14">
+        <v>35</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>855</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>585</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B872C43-16D0-444C-9E7A-5E2B7C3E753B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F9926A0-D3AD-4816-A52C-B21F09A8DD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3129,26 +3129,50 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B52" s="14">
+        <v>480</v>
+      </c>
+      <c r="C52" s="14">
+        <v>40</v>
+      </c>
+      <c r="D52" s="14">
+        <v>120</v>
+      </c>
+      <c r="E52" s="14">
+        <v>60</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>35</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>735</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>705</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F9926A0-D3AD-4816-A52C-B21F09A8DD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD634E1-CFC3-46CC-8E2D-B0B89A0D53FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3175,26 +3175,50 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B53" s="14">
+        <v>480</v>
+      </c>
+      <c r="C53" s="14">
+        <v>40</v>
+      </c>
+      <c r="D53" s="14">
+        <v>120</v>
+      </c>
+      <c r="E53" s="14">
+        <v>60</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>120</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr showObjects="none"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD634E1-CFC3-46CC-8E2D-B0B89A0D53FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2EE2F9B-E985-43F5-B3F4-753B08E07EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3221,26 +3221,50 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B54" s="14">
+        <v>480</v>
+      </c>
+      <c r="C54" s="14">
+        <v>40</v>
+      </c>
+      <c r="D54" s="14">
+        <v>120</v>
+      </c>
+      <c r="E54" s="14">
+        <v>30</v>
+      </c>
+      <c r="F54" s="14">
+        <v>200</v>
+      </c>
+      <c r="G54" s="14">
+        <v>4</v>
+      </c>
+      <c r="H54" s="14">
+        <v>40</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2EE2F9B-E985-43F5-B3F4-753B08E07EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232E57B1-B46B-4EED-8658-6A3BD9983D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3267,26 +3267,50 @@
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B55" s="14">
+        <v>480</v>
+      </c>
+      <c r="C55" s="14">
+        <v>30</v>
+      </c>
+      <c r="D55" s="14">
+        <v>120</v>
+      </c>
+      <c r="E55" s="14">
+        <v>40</v>
+      </c>
+      <c r="F55" s="14">
+        <v>200</v>
+      </c>
+      <c r="G55" s="14">
+        <v>4</v>
+      </c>
+      <c r="H55" s="14">
+        <v>35</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>905</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>535</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232E57B1-B46B-4EED-8658-6A3BD9983D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACF0B06-2487-4B9A-AF70-058D2E7D0202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3313,26 +3313,50 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B56" s="14">
+        <v>480</v>
+      </c>
+      <c r="C56" s="14">
+        <v>30</v>
+      </c>
+      <c r="D56" s="14">
+        <v>60</v>
+      </c>
+      <c r="E56" s="14">
+        <v>60</v>
+      </c>
+      <c r="F56" s="14">
+        <v>200</v>
+      </c>
+      <c r="G56" s="14">
+        <v>4</v>
+      </c>
+      <c r="H56" s="14">
+        <v>60</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACF0B06-2487-4B9A-AF70-058D2E7D0202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456FABD6-7C8B-4EE5-B48E-80C74B50D028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3359,26 +3359,50 @@
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B57" s="14">
+        <v>480</v>
+      </c>
+      <c r="C57" s="14">
+        <v>25</v>
+      </c>
+      <c r="D57" s="14">
+        <v>60</v>
+      </c>
+      <c r="E57" s="14">
+        <v>0</v>
+      </c>
+      <c r="F57" s="14">
+        <v>200</v>
+      </c>
+      <c r="G57" s="14">
+        <v>4</v>
+      </c>
+      <c r="H57" s="14">
+        <v>120</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>885</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>555</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456FABD6-7C8B-4EE5-B48E-80C74B50D028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4835DD36-42C6-4FC2-9965-394B4F876F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t xml:space="preserve">happy day </t>
+  </si>
+  <si>
+    <t>happy days</t>
   </si>
 </sst>
 </file>
@@ -3405,26 +3408,50 @@
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13">
+        <v>46326</v>
+      </c>
+      <c r="B58" s="14">
+        <v>480</v>
+      </c>
+      <c r="C58" s="14">
+        <v>30</v>
+      </c>
+      <c r="D58" s="14">
+        <v>0</v>
+      </c>
+      <c r="E58" s="14">
+        <v>0</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>300</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>
